--- a/GLMER/glmer_Py/ForSimulation_Adults_With_Tokens.xlsx
+++ b/GLMER/glmer_Py/ForSimulation_Adults_With_Tokens.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthi2revithiadou/Desktop/Lg&amp;Sp_reviews/article/revision/Suplemental_materials/glmer_Py/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthi2revithiadou/Desktop/Supplemental_materials/GLMER/glmer_Py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23386E8-9FBA-2541-81F4-D60366CD970F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45A3705-C480-EC4B-93EC-00A95F35081E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="660" windowWidth="28200" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="660" windowWidth="28160" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -632,7 +632,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="D8" s="1">
         <v>4.5502645502645503E-2</v>
